--- a/02_skill/sample_outputs/monthly_review_2026-06.xlsx
+++ b/02_skill/sample_outputs/monthly_review_2026-06.xlsx
@@ -7,25 +7,33 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Commentary Sign-off" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Numbers Check" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Top Movements" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reviewer Changes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Open Questions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Commentary Sign-off" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Numbers Check" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Top Movements" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Data checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Flux Items" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Reviewer Changes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Open Questions" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Commentary Sign-off'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Commentary Sign-off'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Numbers Check'!$A$1:$E$28</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Numbers Check'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Top Movements'!$A$1:$C$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Top Movements'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reviewer Changes'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Reviewer Changes'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Open Questions'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Open Questions'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Cover'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Summary'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Commentary Sign-off'!$A$1:$G$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Commentary Sign-off'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Numbers Check'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Numbers Check'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Top Movements'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Top Movements'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Data checks'!$A$1:$E$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Data checks'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Flux Items'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Flux Items'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Reviewer Changes'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Reviewer Changes'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Open Questions'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Open Questions'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,9 +41,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0)"/>
     <numFmt numFmtId="165" formatCode="0.0;[Red](0.0)"/>
+    <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%)"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -83,12 +92,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -97,22 +121,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -480,11 +495,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,123 +508,223 @@
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ABC Inc</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Reviewer verdict</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>approve</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sign-off status</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Awaiting human approval (nobody has signed off)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Automatic number check</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>27/27 numbers match the JSON</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>$195,898.16</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Top 3 movements named</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>3/3</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Revenue vs same month last year</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>+2.8% vs 2025-06</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Cash risk covered</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Open changes</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>0</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>-$330,756.08</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Final sign-off (name / date)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Net income excluding one-offs</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>-$330,756.08</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Source packet</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>review_packet_2026-06.json</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>$713,481.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Runway</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>3.4 months (3m average burn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Data checks</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>18/18 pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Flux threshold</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Flagged when the month-over-month change is at least $5,000 and 10%; a sign change is flagged from $1,000. Source: client config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Flux items flagged</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Numbers matched</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>46/46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Commentary sections</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>all present, in order</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer checklist</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>numbers 17/17, coverage 12/12, causes 18/18, tone 18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Owner memo</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>graded PASS (21/21 numbers), owner_memo_2026-06.md</t>
         </is>
       </c>
     </row>
@@ -625,7 +740,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ABC Inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer verdict</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Automatic number check</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>46/46 numbers match the JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Top 3 movements named</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Cash risk covered</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Required sections present</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Open changes</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer format problems</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Final sign-off (name / date)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Source packet</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>review_packet_2026-06.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -643,7 +927,7 @@
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
@@ -658,7 +942,7 @@
           <t>Reviewer status</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Reviewer note</t>
         </is>
@@ -675,374 +959,548 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Revenue for 2026-06 was $195,898.16, a decrease of $12,452.80 (-5.98%) from 2026-05.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>all 3 match</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Net income for 2026-06 was -$330,756.08, an improvement of $8,343.52 from 2026-05, at a net margin of -168.84%, down 6.09 percentage points from 2026-05.</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>all 4 match</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Loss shrank (mom_change 8343.52), margin fell 6.09pp because revenue fell; both directions correct.</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>The three largest line-item movements in 2026-06 were Events &amp; Conferences (up $17,970.67), Bad Debts (down $14,741.53, from $12,935.29 to a negative balance of -$1,806.24) and Usage Fees (down $11,142.74), all against 2026-05.</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>all 5 match</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>All three top_movements named; Bad Debts 12,935.29 to -1,806.24 matches.</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Revenue for 2026-06 was $195,898.16, compared with $190,555.65 in 2025-06, an increase of $5,342.51 (+2.80%).</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>all 4 match</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Trailing-twelve-month revenue ended 2026-06 was $2,303,975.51.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>all 1 match</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Gross profit for 2026-06 was $137,425.72, a decrease of $2,255.71 (-1.61%) from 2026-05, at a gross margin of 70.15%, up 3.11 percentage points from 2026-05.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>all 5 match</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Gross margin was 70.15% in 2026-06 against 74.32% in 2025-06, a change of -4.17 percentage points.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>all 3 match</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Trailing-twelve-month net income ended 2026-06 was -$3,089,779.59.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>all 1 match</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Matches months.2026-06.net_income.ttm = -3089779.59.</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Operating expenses for 2026-06 were $468,181.80, a decrease of $10,599.23 (-2.21%) from 2026-05.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>all 3 match</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Net income for 2026-06 was -$330,756.08, an improvement of $8,343.52 from 2026-05, at a net margin of -168.84%, down 6.09 percentage points from 2026-05.</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>all 4 match</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Payroll &amp; Benefits was $331,397.16 in 2026-06 against $356,774.30 in 2025-06 (-7.11%).</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>all 3 match</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Net margin -168.84% and the 6.09pp fall are correct. The loss shrank while revenue fell, so the margin worsened.</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>The largest line-item movement in 2026-06 was Events &amp; Conferences, up $17,970.67 from 2026-05.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing was $74,527.55 in 2026-06 against $80,777.29 in 2025-06 (-7.74%).</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>all 3 match</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Technology was $34,089.48 in 2026-06 against $18,256.59 in 2025-06 (+86.72%).</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>all 3 match</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>The cash balance at 2026-06 was $713,481.26, a decrease of $215,543.33 (-23.20%) from 2026-05.</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>all 3 match</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Runway at 2026-06 was 3.40 months, based on the 3-month average burn of $209,656.62; it uses past balances only and is not a forecast.</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>all 2 match</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Matches cash.runway_months.3m = 3.403094 and cash.burn.3m = 209656.62 (primary window).</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>The packet reports no one-off items in 2026-06, so net income excluding one-offs is -$330,756.08, the same as reported net income.</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>all 1 match</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>No one-off in 2026-06; adjusted_net_income equals net income.</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>The second-largest line-item movement in 2026-06 was Bad Debts, down $14,741.53 from $12,935.29 in 2026-05 to a credit balance of -$1,806.24 in 2026-06.</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>all 3 match</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>The packet reports no data-quality warnings for 2026-06.</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>no numbers</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Bad Debts moved from 12,935.29 to -1,806.24, which is a negative or reversing line. It is named correctly.</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>warnings is empty.</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>The third-largest line-item movement in 2026-06 was Usage Fees, down $11,142.74 from 2026-05.</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Is the Technology increase of $15,832.89 against 2025-06 expected to continue?</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>all 1 match</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Question only; yoy Technology change 15832.89 matches.</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Trailing-twelve-month revenue ended 2026-06 was $2,303,975.51 and trailing-twelve-month net income was -$3,089,779.59.</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>all 2 match</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Is the Events &amp; Conferences amount of $29,294.58 in 2026-06 a single event or several?</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>all 1 match</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Events &amp; Conferences value 29294.58 matches.</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>The cash balance at 2026-06 was $713,481.26, a decrease of $215,543.33 (-23.20%) from 2026-05.</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>all 3 match</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Runway at 2026-06 was 3.40 months, based on the 3-month average burn of $209,656.62.</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>all 2 match</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>runway_months.3m = 3.403094 and burn.3m = 209,656.62, with primary_window = 3m.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>The packet reports no data-quality warnings for 2026-06.</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>no numbers</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>warnings is empty.</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>The packet reports no one-off items in 2026-06.</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>no numbers</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>No entry in one_offs has month 2026-06. The only 2026 item is SKU Profiling in 2026-04.</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
@@ -1069,634 +1527,1071 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>$195,898.16</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>195898.16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="A3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>$12,452.80</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>12452.8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>-5.98%</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>5.9768</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>-$330,756.08</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>330756.08</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>$8,343.52</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>8343.52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>-168.84%</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>168.8408</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>6.09 percentage points</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>pp</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>6.086793</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>$17,970.67)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>17970.67</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>$14,741.53</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>14741.53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>$12,935.29</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>12935.29</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>-$1,806.24)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1806.24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>$11,142.74)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>11142.74</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>$195,898.16</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>195898.16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>$190,555.65</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>190555.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>$5,342.51</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>5342.51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>+2.80%</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>2.7994</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>$2,303,975.51</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>2303975.51</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>$137,425.72</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="n">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>137425.72</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>$2,255.71</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n">
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>2255.71</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>-1.61%</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>1.6149</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>70.15%</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="n">
         <v>70.1516</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>3.11 percentage points</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>3.110199</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>70.15%</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>70.1516</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>74.32%</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>74.32250000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>-4.17 percentage points</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>pp</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>4.170895</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>-$3,089,779.59</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>3089779.59</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>$468,181.80</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="n">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n">
         <v>468181.8</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>$10,599.23</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>10599.23</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>-2.21%</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="n">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="n">
         <v>2.2138</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>$331,397.16</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>331397.16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>$356,774.30</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>356774.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>-7.11%</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>7.1129</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>$74,527.55</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>74527.55</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>$80,777.29</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>80777.28999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>-7.74%</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>7.736999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>$34,089.48</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>34089.48</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>$18,256.59</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>18256.59</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>+86.72%</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>86.7242</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>$713,481.26</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>713481.26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>$215,543.33</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>215543.33</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>-23.20%</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>23.201</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>3.403094</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>$209,656.62</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>209656.62</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>-$330,756.08</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>330756.08</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>$8,343.52</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>$15,832.89</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>8343.52</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>-168.84%</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>168.8408</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>6.09 percentage points</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>pp</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>6.086793</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>$17,970.67</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>15832.89</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>$29,294.58</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>17970.67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>$14,741.53</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>14741.53</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>$12,935.29</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>12935.29</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>-$1,806.24</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>1806.24</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>$11,142.74</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>11142.74</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>$2,303,975.51</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>2303975.51</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>-$3,089,779.59</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>3089779.59</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>$713,481.26</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>713481.26</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>$215,543.33</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>215543.33</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>-23.20%</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>23.201</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>3.403094</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>$209,656.62</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>209656.62</v>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>29294.58</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E28"/>
+  <autoFilter ref="A1:E47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1728,45 +2623,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Events &amp; Conferences</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="10" t="n">
         <v>17970.67</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Bad Debts</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="10" t="n">
         <v>-14741.53</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Usage Fees</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="10" t="n">
         <v>-11142.74</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1779,7 +2674,699 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Fix hint</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Income statement sheet present</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Header row found</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!B5</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Month columns contiguous</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C5:T5</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Total row present: Total Income</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C14</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Total row present: Total Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C24</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Total row present: Gross Profit</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C26</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Total row present: Total Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C103</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Total row present: Operating Income</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C105</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Total row present: Net Income</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C107</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Every amount is a number</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Gross profit = revenue - COGS (every month)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Operating income = gross profit - opex (every month)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Total Income foots to its lines (every month)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Total Cost of Goods Sold foots to its lines (every month)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses foots to its lines (every month)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Balance Sheet rows present</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Balance Sheet balances (assets = liabilities + equity, every month)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Current Year Earnings = year-to-date net income (every month)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Prior</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Source cell</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Why flagged</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Events &amp; Conferences</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>operating expenses</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>LARGE_MOVE</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>29294.58</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>11323.91</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>17970.67</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>1.586967</v>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C65</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>|$Δ| &gt;= $5,000 and |%Δ| &gt;= 10%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Bad Debts</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>operating expenses</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>SIGN_FLIP</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>-1806.24</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>12935.29</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>-14741.53</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>-1.139637</v>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C31</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Sign changed versus prior month. Flagged when |$Δ| &gt;= $1,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Partnerships Commission</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>operating expenses</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>LARGE_MOVE</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>-0.833333</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C97</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>|$Δ| &gt;= $5,000 and |%Δ| &gt;= 10%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Marketing/Advertising: Partner Marketing</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>operating expenses</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>LARGE_MOVE</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>4020.45</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>12415.08</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>-8394.629999999999</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>-0.676164</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C70</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>|$Δ| &gt;= $5,000 and |%Δ| &gt;= 10%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sales Commission</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>cost of goods sold</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>LARGE_MOVE</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>5926.88</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>13126.41</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>-7199.53</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>-0.548477</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Income Statement!C23</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>|$Δ| &gt;= $5,000 and |%Δ| &gt;= 10%.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1795,7 +3382,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
@@ -1805,26 +3392,26 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Suggested fix</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D2"/>
@@ -1833,7 +3420,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1862,12 +3449,12 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Why it matters</t>
         </is>
@@ -1877,7 +3464,7 @@
           <t>Owner</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
@@ -1889,135 +3476,135 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>What explains the Bad Debts credit of -1,806.24 in June, against 12,935.29 in May? Is it a recovery or reversal of a prior provision?</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>It is the second-largest movement and cuts operating expenses by 14.7k. If it is non-recurring, underlying operating expenses are higher than reported.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="7" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>What explains the Bad Debts swing from 12,935.29 to -1,806.24 (a recovery or reversal)?</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>A 14,741.53 credit reduced June operating expenses and improved net income.</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>What is the nature of the Events &amp; Conferences increase, from 11,323.91 to 29,294.58? Is it one-off or recurring?</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>It is the largest movement and, at 6.3% of operating expenses, the main offset to the other cost reductions.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Why did cash fall 215,543.33 (-23.2%) in June, and are further drawdowns or funding planned?</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Runway is 3.40 months on the 3-month burn (3.31 on 1-month, 2.29 on 6-month), so the balance is the key sensitivity.</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Why did Partnership Income and Professional Services fall to zero, and why did Usage Fees fall 6.3%?</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>These three lines account for the whole 12.5k revenue decline (-476.73, -833.33 and -11,142.74). Whether they continue matters for runway.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="7" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Is the Technology increase (+86.72% vs 2025-06) a new recurring cost?</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>It adds 15,832.89 year on year to the run-rate.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Is the drop in Partnerships Commission (10,800 to 1,800) and Sales Commission (13,126.41 to 5,926.88) a timing difference?</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>These lines drive much of the cost reduction and may reverse next month.</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Is the December 2025 Income Tax Benefit (-1,244,429.84) and stock-based compensation (334,660.53) to be treated as one-offs when reading TTM net income of -3,089,779.59?</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Both sit inside the TTM window and distort it.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Auto (cash)</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Runway is 3.4 months at the 3m average burn (cash 713,481.26). Is there a funding plan or forecast to compare with?</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Runway is derived from past balance changes only; no forecast was supplied.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
